--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_944_Mexico_Atlantic.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_944_Mexico_Atlantic.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rccef438fc8414be8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R49649db7dc9e4547"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc16dae7a8a474b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R8cd0b781b9344e50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R13a1df244b43446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4d316a2c63534cb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R0477979dea194d54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rcd3c50150df34e9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc78303b594b448c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc5cdb286b5bd4e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R95d10ff4ea384df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R1a3942ae0678424b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ944CommercialTable" displayName="EEZ944CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ944CommercialTable" displayName="EEZ944CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ944FunctionalTable" displayName="EEZ944FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ944FunctionalTable" displayName="EEZ944FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ944ValidationTable" displayName="EEZ944ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ944ValidationTable" displayName="EEZ944ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7595,7 +7549,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reeea1e835a9446a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d9bba746ab247b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7605,20 +7559,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7626,606 +7570,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>248.8115709529</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>248.8115709529</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$104,A2,'Species'!$U$2:$U$104))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>39433.97650088067</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>39433.97650088067</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>363.8842241223</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.91</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>812.8305161640995</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>363.8842241223</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>812.8305161640994</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$104,A3,'Species'!$U$2:$U$104))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>295776.20171730197</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.91</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>812.8305161640995</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>295776.20171730197</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>56163.52587311821</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1434457529753863</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>139.13799889553934</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>56163.52587311821</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>376.8246487784298</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$104,A4,'Species'!$U$2:$U$104))</x:f>
-        <x:v>21163800.911296025</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1434457529753863</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>139.13799889553934</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>7814480.600903517</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>13349320.310392508</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>2.708279921873381</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>1.7082799218733806</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>97</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$104,A5,'Species'!$U$2:$U$104))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>36038.91722242573</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>36038.91722242573</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>4.0036605365</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.42</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>263.02679918953817</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>4.0036605365</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>263.02679918953817</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$104,A6,'Species'!$U$2:$U$104))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1053.0700159570642</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.42</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>263.02679918953817</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>1053.0700159570642</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>57677.6458086829</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.1055266948674802</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.750484711994448</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>57677.6458086829</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>20.035170038064365</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$104,A7,'Species'!$U$2:$U$104))</x:f>
-        <x:v>1155581.4411722124</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.1055266948674802</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.750484711994448</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>735417.9411074419</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>420163.50006477046</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5713261488182624</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5713261488182624</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>257225.1097427739</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4793330349185174</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>301.53174075770795</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>257225.1097427739</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>359.88809661239264</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$104,A8,'Species'!$U$2:$U$104))</x:f>
-        <x:v>92572255.14624071</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4793330349185174</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>301.53174075770795</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>77561535.10733108</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>15010720.038909629</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1935330446739807</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.1935330446739807</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>123077.4882099929</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8573463141219584</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>720.0229081786197</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>123077.4882099929</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1300.5193273737073</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$104,A9,'Species'!$U$2:$U$104))</x:f>
-        <x:v>160064652.18170536</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8573463141219584</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>720.0229081786197</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>88618610.99227886</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>71446041.1894265</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.8062193752467124</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.8062193752467124</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>13258.6850305423</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9594844716863093</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>910.9288811813344</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>13258.6850305423</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1191.0465333039815</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$104,A10,'Species'!$U$2:$U$104))</x:f>
-        <x:v>15791710.8417968</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9594844716863093</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>910.9288811813344</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>12077719.120807603</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3713991.7209891975</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.3075077076921502</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.3075077076921502</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>4955.119618286099</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.485765840943786</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>3060.3129563229327</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>4955.119618286099</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3068.550297771156</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$104,A11,'Species'!$U$2:$U$104))</x:f>
-        <x:v>15205033.780183503</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.485765840943786</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>3060.3129563229327</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>15164216.767970892</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>40817.012212611735</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0026916663641225</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.002691666364122637</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf64c8715306c43a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f011cf4c7214927"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8235,20 +7785,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8256,1092 +7796,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>35980.5926887781</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.5398520394703565</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>346.6187402027966</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>35980.5926887781</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>348.85837863088017</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$104,A2,'Species'!$U$2:$U$104))</x:f>
-        <x:v>12552131.22758523</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.5398520394703565</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>346.6187402027966</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>12471547.709534219</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>80583.51805101149</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0064613887488405</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.006461388748840466</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>8558.6640564234</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.784234798647017</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>60.84638746296017</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>8558.6640564234</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>463.0890864762719</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$104,A3,'Species'!$U$2:$U$104))</x:f>
-        <x:v>3963423.9193464164</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.784234798647017</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>60.84638746296017</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>520763.78934244864</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3442660.130003968</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>7.610790151809329</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>6.610790151809329</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>338.5857264744</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.88255727633223</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>763.0575193203949</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>338.5857264744</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>763.822216217954</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$104,A4,'Species'!$U$2:$U$104))</x:f>
-        <x:v>258619.29997544218</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.88255727633223</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>763.0575193203949</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>258360.38452084945</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>258.9154545927304</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.001002148433371</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0010021484333711237</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>8922.748675375298</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.3867255744226945</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2436.2708809583064</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>8922.748675375298</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2505.8035559644172</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$104,A5,'Species'!$U$2:$U$104))</x:f>
-        <x:v>22358655.359732214</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.3867255744226945</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2436.2708809583064</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>21738232.77592614</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>620422.5838060752</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.028540617363025</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.028540617363024927</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3597.8340695031</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.4079567044193744</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>255.83308296929638</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3597.8340695031</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>263.3113529502909</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$104,A6,'Species'!$U$2:$U$104))</x:f>
-        <x:v>947350.5565315122</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.4079567044193744</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>255.83308296929638</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>920444.9820129479</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>26905.574518564274</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0292310513331537</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.029231051333153766</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>9354.1437420739</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.9199999999999995</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>831.76377110267</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>9354.1437420739</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$104,A7,'Species'!$U$2:$U$104))</x:f>
-        <x:v>7780437.874343837</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.9199999999999995</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>831.76377110267</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>7780437.874343829</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>7.450580596923828e-9</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>9.576042784805579e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>9660.8509610392</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.164881014843053</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1461.7766316052198</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>9660.8509610392</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1536.5479029880935</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$104,A8,'Species'!$U$2:$U$104))</x:f>
-        <x:v>14844360.28526529</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.164881014843053</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1461.7766316052198</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>14122006.176267931</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>722354.108997358</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0511509554649023</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.05115095546490243</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>20061.8970059378</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9613974642668466</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>914.9502165481151</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>20061.8970059378</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>959.3944423454595</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$104,A9,'Species'!$U$2:$U$104))</x:f>
-        <x:v>19247272.49040374</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9613974642668466</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>914.9502165481151</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>18355637.00994877</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>891635.4804549702</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0485755672751484</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.04857556727514839</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>6275.3320046517</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.2216874359185974</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>16.660477174316497</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>6275.3320046517</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>71.91698697330838</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$104,A10,'Species'!$U$2:$U$104))</x:f>
-        <x:v>451302.9700317215</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.2216874359185974</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>16.660477174316497</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>104550.02562475744</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>346752.94440696406</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>4.316622280433502</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>3.3166222804335015</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>226664.54499035285</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.509786515971799</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>323.4346286576361</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>226664.54499035285</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>416.22493636527946</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$104,A11,'Species'!$U$2:$U$104))</x:f>
-        <x:v>94343435.81487463</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.509786515971799</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>323.4346286576361</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>73311162.93880682</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>21032272.876067817</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2868904547814028</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.2868904547814029</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>26778.9568431323</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.147923960945532</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1405.8013658902075</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>26778.9568431323</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2238.830720703716</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$104,A12,'Species'!$U$2:$U$104))</x:f>
-        <x:v>59953551.24880359</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.147923960945532</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1405.8013658902075</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>37645894.1071903</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>22307657.14161329</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.5925654754830902</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.5925654754830904</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>56898.390927718596</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.9991601461513313</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>998.0680337018227</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>56898.390927718596</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1154.7103417862088</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$104,A13,'Species'!$U$2:$U$104))</x:f>
-        <x:v>65701160.43523126</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.9991601461513313</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>998.0680337018227</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>56788465.154025726</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>8912695.281205535</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.1569455215426563</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.15694552154265637</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>59175.6458086829</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.1028553427132075</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>12.672296994460368</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>59175.6458086829</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>19.78113504593903</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$104,A14,'Species'!$U$2:$U$104))</x:f>
-        <x:v>1170561.4411722124</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.1028553427132075</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>12.672296994460368</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>749891.3585266236</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>420670.0826455888</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.5609747036852322</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.5609747036852321</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>36101.62886718041</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.6889049606989004</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>48.854543627676776</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>36101.62886718041</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>53.08703460287851</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$104,A15,'Species'!$U$2:$U$104))</x:f>
-        <x:v>1916528.420892284</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.6889049606989004</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>48.854543627676776</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1763728.6025218605</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>152799.8183704235</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0866345412508156</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.08663454125081563</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>1568.0167545165</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.0299999999999994</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>107.15193052376048</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>1568.0167545165</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$104,A16,'Species'!$U$2:$U$104))</x:f>
-        <x:v>168016.02234004458</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.0299999999999994</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>107.15193052376048</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>168016.0223400444</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1.7462298274040222e-10</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>1.0393233949259085e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>422.5475029932</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.61</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>407.3802778041126</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>422.5475029932</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$104,A17,'Species'!$U$2:$U$104))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>172137.51915480391</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.61</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>172137.51915480391</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>252.81523148940002</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.2034839883374153</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>159.76586251501882</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>252.81523148940002</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>160.14480725040994</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$104,A18,'Species'!$U$2:$U$104))</x:f>
-        <x:v>40487.046516837734</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.2034839883374153</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>159.76586251501882</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>40391.24351583814</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>95.80300099959277</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0023718755022244</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0023718755022243045</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>2361.077882685</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.25</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>177.82794100389228</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>2361.077882685</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>177.82794100389228</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$104,A19,'Species'!$U$2:$U$104))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>419865.6184277031</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.25</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>177.82794100389228</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>419865.6184277031</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>97</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.57</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>371.5352290971724</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$104,A20,'Species'!$U$2:$U$104))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>36038.91722242573</x:v>
       </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.57</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>371.5352290971724</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>36038.91722242573</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8cf7514a8a443a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03363224fb74406c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9516,7 +8347,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9615,7 +8446,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>306325336.46785116</x:v>
+        <x:v>202344282.69585595</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9629,7 +8460,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>306325336.4678512</x:v>
+        <x:v>247367572.20925406</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9643,7 +8474,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.1920928955078125e-7</x:v>
+        <x:v>-103981053.77199534</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9657,7 +8488,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-58957764.258597225</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9668,9 +8499,9 @@
         <x:v>EEZ_944</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9682,47 +8513,19 @@
         <x:v>EEZ_944</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_944</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_944</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5023b24eebe94a62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7edc498585eb4f80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9769,7 +8572,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
